--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/OKLAHOMA_2019.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/OKLAHOMA_2019.xlsx
@@ -2706,7 +2706,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C131">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C181">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C282">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C658">
